--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -928,7 +928,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.72</t>
+          <t>£14.70</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£23.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£33.26</t>
+          <t>£33.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£41.32</t>
+          <t>£41.30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff68cbea235
-	0x7ff68c942630
-	0x7ff68c6d16dd
-	0x7ff68c72a27e
-	0x7ff68c72a58c
-	0x7ff68c77ed77
-	0x7ff68c77baba
-	0x7ff68c71b0ed
-	0x7ff68c71bf63
-	0x7ff68cc15d60
-	0x7ff68cc0fe8a
-	0x7ff68cc31005
-	0x7ff68c95d71e
-	0x7ff68c964e1f
-	0x7ff68c94b7c4
-	0x7ff68c94b97f
-	0x7ff68c9318e8
+	0x7ff758b8a235
+	0x7ff7588e2630
+	0x7ff7586716dd
+	0x7ff7586ca27e
+	0x7ff7586ca58c
+	0x7ff75871ed77
+	0x7ff75871baba
+	0x7ff7586bb0ed
+	0x7ff7586bbf63
+	0x7ff758bb5d60
+	0x7ff758bafe8a
+	0x7ff758bd1005
+	0x7ff7588fd71e
+	0x7ff758904e1f
+	0x7ff7588eb7c4
+	0x7ff7588eb97f
+	0x7ff7588d18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
